--- a/data/04-12-2025-employee_designations.xlsx
+++ b/data/04-12-2025-employee_designations.xlsx
@@ -1611,7 +1611,7 @@
         <v>45879</v>
       </c>
       <c r="F2" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1631,7 +1631,7 @@
         <v>45879</v>
       </c>
       <c r="F3" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
         <v>45879</v>
       </c>
       <c r="F4" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
         <v>45879</v>
       </c>
       <c r="F5" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1691,7 +1691,7 @@
         <v>45879</v>
       </c>
       <c r="F6" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1711,7 +1711,7 @@
         <v>45879</v>
       </c>
       <c r="F7" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1731,7 +1731,7 @@
         <v>45879</v>
       </c>
       <c r="F8" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1751,7 +1751,7 @@
         <v>45879</v>
       </c>
       <c r="F9" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1771,7 +1771,7 @@
         <v>45879</v>
       </c>
       <c r="F10" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,7 +1791,7 @@
         <v>45879</v>
       </c>
       <c r="F11" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
         <v>45879</v>
       </c>
       <c r="F12" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,7 +1831,7 @@
         <v>45879</v>
       </c>
       <c r="F13" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1851,7 +1851,7 @@
         <v>45879</v>
       </c>
       <c r="F14" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1871,7 +1871,7 @@
         <v>45879</v>
       </c>
       <c r="F15" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1891,7 +1891,7 @@
         <v>45879</v>
       </c>
       <c r="F16" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1911,7 +1911,7 @@
         <v>45879</v>
       </c>
       <c r="F17" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1931,7 +1931,7 @@
         <v>45879</v>
       </c>
       <c r="F18" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1951,7 +1951,7 @@
         <v>45879</v>
       </c>
       <c r="F19" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1971,7 +1971,7 @@
         <v>45879</v>
       </c>
       <c r="F20" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
         <v>45879</v>
       </c>
       <c r="F21" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2011,7 +2011,7 @@
         <v>45879</v>
       </c>
       <c r="F22" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2031,7 +2031,7 @@
         <v>45879</v>
       </c>
       <c r="F23" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2051,7 +2051,7 @@
         <v>45879</v>
       </c>
       <c r="F24" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2071,7 +2071,7 @@
         <v>45879</v>
       </c>
       <c r="F25" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2091,7 +2091,7 @@
         <v>45879</v>
       </c>
       <c r="F26" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,7 +2111,7 @@
         <v>45879</v>
       </c>
       <c r="F27" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2131,7 +2131,7 @@
         <v>45879</v>
       </c>
       <c r="F28" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,7 +2151,7 @@
         <v>45879</v>
       </c>
       <c r="F29" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,7 +2171,7 @@
         <v>45879</v>
       </c>
       <c r="F30" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2191,7 +2191,7 @@
         <v>45879</v>
       </c>
       <c r="F31" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>45879</v>
       </c>
       <c r="F32" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,7 +2231,7 @@
         <v>45879</v>
       </c>
       <c r="F33" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,7 +2251,7 @@
         <v>45879</v>
       </c>
       <c r="F34" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2271,7 +2271,7 @@
         <v>45879</v>
       </c>
       <c r="F35" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2291,7 +2291,7 @@
         <v>45879</v>
       </c>
       <c r="F36" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2311,7 +2311,7 @@
         <v>45879</v>
       </c>
       <c r="F37" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2331,7 +2331,7 @@
         <v>45879</v>
       </c>
       <c r="F38" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,7 +2351,7 @@
         <v>45879</v>
       </c>
       <c r="F39" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2371,7 +2371,7 @@
         <v>45879</v>
       </c>
       <c r="F40" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2391,7 +2391,7 @@
         <v>45879</v>
       </c>
       <c r="F41" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2409,7 +2409,7 @@
         <v>45879</v>
       </c>
       <c r="F42" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2427,7 +2427,7 @@
         <v>45879</v>
       </c>
       <c r="F43" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
         <v>45879</v>
       </c>
       <c r="F44" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,7 +2463,7 @@
         <v>45879</v>
       </c>
       <c r="F45" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2481,7 +2481,7 @@
         <v>45879</v>
       </c>
       <c r="F46" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,7 +2499,7 @@
         <v>45879</v>
       </c>
       <c r="F47" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2517,7 +2517,7 @@
         <v>45879</v>
       </c>
       <c r="F48" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2535,7 +2535,7 @@
         <v>45879</v>
       </c>
       <c r="F49" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,7 +2553,7 @@
         <v>45879</v>
       </c>
       <c r="F50" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2571,7 +2571,7 @@
         <v>45879</v>
       </c>
       <c r="F51" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2589,7 +2589,7 @@
         <v>45879</v>
       </c>
       <c r="F52" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2607,7 +2607,7 @@
         <v>45879</v>
       </c>
       <c r="F53" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2625,7 +2625,7 @@
         <v>45879</v>
       </c>
       <c r="F54" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,7 +2643,7 @@
         <v>45879</v>
       </c>
       <c r="F55" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2661,7 +2661,7 @@
         <v>45879</v>
       </c>
       <c r="F56" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2679,7 +2679,7 @@
         <v>45879</v>
       </c>
       <c r="F57" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2697,7 +2697,7 @@
         <v>45879</v>
       </c>
       <c r="F58" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2717,7 +2717,7 @@
         <v>45879</v>
       </c>
       <c r="F59" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2737,7 +2737,7 @@
         <v>45879</v>
       </c>
       <c r="F60" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2755,7 +2755,7 @@
         <v>45879</v>
       </c>
       <c r="F61" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,7 +2775,7 @@
         <v>45879</v>
       </c>
       <c r="F62" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
         <v>45879</v>
       </c>
       <c r="F63" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2811,7 +2811,7 @@
         <v>45879</v>
       </c>
       <c r="F64" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2831,7 +2831,7 @@
         <v>45879</v>
       </c>
       <c r="F65" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2851,7 +2851,7 @@
         <v>45879</v>
       </c>
       <c r="F66" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2871,7 +2871,7 @@
         <v>45879</v>
       </c>
       <c r="F67" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2891,7 +2891,7 @@
         <v>45879</v>
       </c>
       <c r="F68" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2909,7 +2909,7 @@
         <v>45879</v>
       </c>
       <c r="F69" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>45879</v>
       </c>
       <c r="F70" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2945,7 +2945,7 @@
         <v>45879</v>
       </c>
       <c r="F71" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,7 +2963,7 @@
         <v>45879</v>
       </c>
       <c r="F72" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,7 +2981,7 @@
         <v>45879</v>
       </c>
       <c r="F73" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +3001,7 @@
         <v>45879</v>
       </c>
       <c r="F74" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,7 +3021,7 @@
         <v>45879</v>
       </c>
       <c r="F75" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,7 +3039,7 @@
         <v>45879</v>
       </c>
       <c r="F76" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,7 +3059,7 @@
         <v>45879</v>
       </c>
       <c r="F77" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,7 +3079,7 @@
         <v>45879</v>
       </c>
       <c r="F78" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3099,7 +3099,7 @@
         <v>45879</v>
       </c>
       <c r="F79" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
         <v>45879</v>
       </c>
       <c r="F80" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3139,7 +3139,7 @@
         <v>45879</v>
       </c>
       <c r="F81" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,7 +3159,7 @@
         <v>45879</v>
       </c>
       <c r="F82" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3179,7 +3179,7 @@
         <v>45879</v>
       </c>
       <c r="F83" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3199,7 +3199,7 @@
         <v>45879</v>
       </c>
       <c r="F84" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3219,7 +3219,7 @@
         <v>45879</v>
       </c>
       <c r="F85" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3239,7 +3239,7 @@
         <v>45879</v>
       </c>
       <c r="F86" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3259,7 +3259,7 @@
         <v>45879</v>
       </c>
       <c r="F87" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3279,7 +3279,7 @@
         <v>45879</v>
       </c>
       <c r="F88" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3299,7 +3299,7 @@
         <v>45879</v>
       </c>
       <c r="F89" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3319,7 +3319,7 @@
         <v>45879</v>
       </c>
       <c r="F90" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3339,7 +3339,7 @@
         <v>45879</v>
       </c>
       <c r="F91" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3359,7 +3359,7 @@
         <v>45879</v>
       </c>
       <c r="F92" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3379,7 +3379,7 @@
         <v>45879</v>
       </c>
       <c r="F93" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3399,7 +3399,7 @@
         <v>45879</v>
       </c>
       <c r="F94" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3419,7 +3419,7 @@
         <v>45879</v>
       </c>
       <c r="F95" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3439,7 +3439,7 @@
         <v>45879</v>
       </c>
       <c r="F96" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>45879</v>
       </c>
       <c r="F97" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3479,7 +3479,7 @@
         <v>45879</v>
       </c>
       <c r="F98" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3499,7 +3499,7 @@
         <v>45879</v>
       </c>
       <c r="F99" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3519,7 +3519,7 @@
         <v>45879</v>
       </c>
       <c r="F100" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3539,7 +3539,7 @@
         <v>45879</v>
       </c>
       <c r="F101" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3559,7 +3559,7 @@
         <v>45879</v>
       </c>
       <c r="F102" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3579,7 +3579,7 @@
         <v>45879</v>
       </c>
       <c r="F103" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3599,7 +3599,7 @@
         <v>45879</v>
       </c>
       <c r="F104" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3619,7 +3619,7 @@
         <v>45879</v>
       </c>
       <c r="F105" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,7 +3639,7 @@
         <v>45879</v>
       </c>
       <c r="F106" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3659,7 +3659,7 @@
         <v>45879</v>
       </c>
       <c r="F107" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3679,7 +3679,7 @@
         <v>45879</v>
       </c>
       <c r="F108" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3699,7 +3699,7 @@
         <v>45879</v>
       </c>
       <c r="F109" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3719,7 +3719,7 @@
         <v>45879</v>
       </c>
       <c r="F110" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,7 +3739,7 @@
         <v>45879</v>
       </c>
       <c r="F111" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3759,7 +3759,7 @@
         <v>45879</v>
       </c>
       <c r="F112" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3779,7 +3779,7 @@
         <v>45879</v>
       </c>
       <c r="F113" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3799,7 +3799,7 @@
         <v>45879</v>
       </c>
       <c r="F114" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,7 +3819,7 @@
         <v>45879</v>
       </c>
       <c r="F115" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3839,7 +3839,7 @@
         <v>45879</v>
       </c>
       <c r="F116" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3859,7 +3859,7 @@
         <v>45879</v>
       </c>
       <c r="F117" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3879,7 +3879,7 @@
         <v>45879</v>
       </c>
       <c r="F118" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3899,7 +3899,7 @@
         <v>45879</v>
       </c>
       <c r="F119" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3919,7 +3919,7 @@
         <v>45879</v>
       </c>
       <c r="F120" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,7 +3939,7 @@
         <v>45879</v>
       </c>
       <c r="F121" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,7 +3959,7 @@
         <v>45879</v>
       </c>
       <c r="F122" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,7 +3979,7 @@
         <v>45879</v>
       </c>
       <c r="F123" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3999,7 +3999,7 @@
         <v>45879</v>
       </c>
       <c r="F124" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>45879</v>
       </c>
       <c r="F125" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4039,7 +4039,7 @@
         <v>45879</v>
       </c>
       <c r="F126" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4059,7 +4059,7 @@
         <v>45879</v>
       </c>
       <c r="F127" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4079,7 +4079,7 @@
         <v>45879</v>
       </c>
       <c r="F128" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,7 +4099,7 @@
         <v>45879</v>
       </c>
       <c r="F129" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>45879</v>
       </c>
       <c r="F130" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4139,7 +4139,7 @@
         <v>45879</v>
       </c>
       <c r="F131" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,7 +4159,7 @@
         <v>45879</v>
       </c>
       <c r="F132" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4179,7 +4179,7 @@
         <v>45879</v>
       </c>
       <c r="F133" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,7 +4199,7 @@
         <v>45879</v>
       </c>
       <c r="F134" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4219,7 +4219,7 @@
         <v>45879</v>
       </c>
       <c r="F135" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4239,7 +4239,7 @@
         <v>45879</v>
       </c>
       <c r="F136" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4259,7 +4259,7 @@
         <v>45879</v>
       </c>
       <c r="F137" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,7 +4279,7 @@
         <v>45879</v>
       </c>
       <c r="F138" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4299,7 +4299,7 @@
         <v>45879</v>
       </c>
       <c r="F139" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,7 +4319,7 @@
         <v>45879</v>
       </c>
       <c r="F140" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,7 +4339,7 @@
         <v>45879</v>
       </c>
       <c r="F141" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4359,7 +4359,7 @@
         <v>45879</v>
       </c>
       <c r="F142" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4379,7 +4379,7 @@
         <v>45879</v>
       </c>
       <c r="F143" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4399,7 +4399,7 @@
         <v>45879</v>
       </c>
       <c r="F144" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,7 +4419,7 @@
         <v>45879</v>
       </c>
       <c r="F145" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,7 +4439,7 @@
         <v>45879</v>
       </c>
       <c r="F146" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,7 +4459,7 @@
         <v>45879</v>
       </c>
       <c r="F147" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,7 +4479,7 @@
         <v>45879</v>
       </c>
       <c r="F148" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
         <v>45879</v>
       </c>
       <c r="F149" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4519,7 +4519,7 @@
         <v>45879</v>
       </c>
       <c r="F150" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4539,7 +4539,7 @@
         <v>45879</v>
       </c>
       <c r="F151" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,7 +4559,7 @@
         <v>45879</v>
       </c>
       <c r="F152" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,7 +4579,7 @@
         <v>45879</v>
       </c>
       <c r="F153" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,7 +4599,7 @@
         <v>45879</v>
       </c>
       <c r="F154" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,7 +4619,7 @@
         <v>45879</v>
       </c>
       <c r="F155" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,7 +4639,7 @@
         <v>45879</v>
       </c>
       <c r="F156" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,7 +4659,7 @@
         <v>45879</v>
       </c>
       <c r="F157" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4679,7 +4679,7 @@
         <v>45879</v>
       </c>
       <c r="F158" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,7 +4699,7 @@
         <v>45879</v>
       </c>
       <c r="F159" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,7 +4719,7 @@
         <v>45879</v>
       </c>
       <c r="F160" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4739,7 +4739,7 @@
         <v>45879</v>
       </c>
       <c r="F161" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,7 +4759,7 @@
         <v>45879</v>
       </c>
       <c r="F162" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4779,7 +4779,7 @@
         <v>45879</v>
       </c>
       <c r="F163" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4799,7 +4799,7 @@
         <v>45879</v>
       </c>
       <c r="F164" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,7 +4819,7 @@
         <v>45879</v>
       </c>
       <c r="F165" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4839,7 +4839,7 @@
         <v>45879</v>
       </c>
       <c r="F166" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4859,7 +4859,7 @@
         <v>45879</v>
       </c>
       <c r="F167" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,7 +4879,7 @@
         <v>45879</v>
       </c>
       <c r="F168" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,7 +4899,7 @@
         <v>45879</v>
       </c>
       <c r="F169" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,7 +4919,7 @@
         <v>45879</v>
       </c>
       <c r="F170" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,7 +4939,7 @@
         <v>45879</v>
       </c>
       <c r="F171" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4959,7 +4959,7 @@
         <v>45879</v>
       </c>
       <c r="F172" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,7 +4979,7 @@
         <v>45879</v>
       </c>
       <c r="F173" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,7 +4999,7 @@
         <v>45879</v>
       </c>
       <c r="F174" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,7 +5019,7 @@
         <v>45879</v>
       </c>
       <c r="F175" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,7 +5039,7 @@
         <v>45879</v>
       </c>
       <c r="F176" s="3">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,7 +5057,7 @@
         <v>45879</v>
       </c>
       <c r="F177" s="6">
-        <v>45989</v>
+        <v>45995.52494815973</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,10 +5074,10 @@
         <v>9</v>
       </c>
       <c r="E178" s="3">
-        <v>45995.40362376157</v>
+        <v>45995</v>
       </c>
       <c r="F178" s="3">
-        <v>45995.40362376157</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,10 +5094,10 @@
         <v>9</v>
       </c>
       <c r="E179" s="6">
-        <v>45995.40459818287</v>
+        <v>45995</v>
       </c>
       <c r="F179" s="6">
-        <v>45995.40459818287</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,10 +5114,10 @@
         <v>9</v>
       </c>
       <c r="E180" s="3">
-        <v>45995.405635138886</v>
+        <v>45995</v>
       </c>
       <c r="F180" s="3">
-        <v>45995.405635138886</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,10 +5134,10 @@
         <v>9</v>
       </c>
       <c r="E181" s="6">
-        <v>45995.406463900465</v>
+        <v>45995</v>
       </c>
       <c r="F181" s="6">
-        <v>45995.406463900465</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5154,10 +5154,10 @@
         <v>9</v>
       </c>
       <c r="E182" s="3">
-        <v>45995.40719763889</v>
+        <v>45995</v>
       </c>
       <c r="F182" s="3">
-        <v>45995.40719763889</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5174,10 +5174,10 @@
         <v>9</v>
       </c>
       <c r="E183" s="9">
-        <v>45995.45175688657</v>
+        <v>45995</v>
       </c>
       <c r="F183" s="9">
-        <v>45995.45175688657</v>
+        <v>45995</v>
       </c>
     </row>
   </sheetData>
